--- a/jogos_2024-09-19.xlsx
+++ b/jogos_2024-09-19.xlsx
@@ -891,35 +891,35 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="P4" t="n">
         <v>2.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="T4" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X4" t="n">
-        <v>2.73</v>
+        <v>3.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.72</v>
+        <v>3.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AD4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['-1']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['-1', '-1']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI4" t="n">
         <v>1.73</v>
       </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>['11', '19']</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>['25', '71']</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AJ4" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45554.47916666666</v>
@@ -1020,35 +1020,35 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="P5" t="n">
         <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="R5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['11', '19']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['25', '71']</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AI5" t="n">
         <v>1.44</v>
       </c>
-      <c r="S5" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>['-1']</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>['-1', '-1']</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45554.47916666666</v>
@@ -1149,35 +1149,35 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Lahti</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
         <v>2</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
         <v>3.25</v>
       </c>
       <c r="O6" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.75</v>
+        <v>4.16</v>
       </c>
       <c r="R6" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>2.78</v>
+        <v>2.91</v>
       </c>
       <c r="T6" t="n">
-        <v>2.77</v>
+        <v>3.05</v>
       </c>
       <c r="U6" t="n">
         <v>1.38</v>
       </c>
       <c r="V6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="X6" t="n">
-        <v>3.12</v>
+        <v>3.32</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.4</v>
+        <v>3.57</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['85', '83', '90+5']</t>
+          <t>['8', '12']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['4', '48']</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45554.5</v>
@@ -1278,119 +1278,119 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
         <v>2</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
         <v>3.25</v>
       </c>
       <c r="O7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T7" t="n">
         <v>2.77</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.05</v>
       </c>
       <c r="U7" t="n">
         <v>1.38</v>
       </c>
       <c r="V7" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W7" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="X7" t="n">
-        <v>3.32</v>
+        <v>3.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.57</v>
+        <v>3.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['8', '12']</t>
+          <t>['85', '83', '90+5']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>['4', '48']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45554.5</v>
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ironi Ramat HaSharon</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,28 +1701,28 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="O10" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T10" t="n">
         <v>2.63</v>
@@ -1737,47 +1737,47 @@
         <v>1.22</v>
       </c>
       <c r="X10" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['18', '48', '90+7']</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['71']</t>
+          <t>['32', '39']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45554.54166666666</v>
@@ -1804,109 +1804,109 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.48</v>
+        <v>2.45</v>
       </c>
       <c r="M11" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>5.25</v>
+        <v>2.45</v>
       </c>
       <c r="O11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD11" t="n">
         <v>2</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['37']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '74', '90+1', '90+2']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.05</v>
+        <v>1.37</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3.4</v>
+        <v>1.95</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45554.54166666666</v>
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Ironi Ramat HaSharon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" t="n">
-        <v>2</v>
-      </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,28 +1959,28 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.63</v>
+        <v>1.95</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
         <v>2.63</v>
@@ -1995,47 +1995,47 @@
         <v>1.22</v>
       </c>
       <c r="X12" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>['18', '48', '90+7']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['32', '39']</t>
+          <t>['71']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45554.54166666666</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,65 +2088,65 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="O13" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="V13" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.37</v>
+        <v>1.13</v>
       </c>
       <c r="X13" t="n">
-        <v>2.85</v>
+        <v>4.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.7</v>
+        <v>2.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AD13" t="n">
         <v>1.83</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['29']</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AJ13" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45554.54166666666</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,109 +2191,109 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['29']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>3</v>
-      </c>
-      <c r="H14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="M14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="O14" t="n">
-        <v>4</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>['18', '45', '73']</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>['13', '68', '79', '87']</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.62</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45554.54166666666</v>
@@ -2320,22 +2320,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
         <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2346,43 +2346,43 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
         <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="V15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="X15" t="n">
-        <v>3.14</v>
+        <v>3.65</v>
       </c>
       <c r="Y15" t="n">
         <v>1.95</v>
@@ -2391,38 +2391,38 @@
         <v>1.85</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.02</v>
+        <v>2.78</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18', '45', '73']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['13', '74', '90+1', '90+2']</t>
+          <t>['13', '68', '79', '87']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45554.54166666666</v>
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M16" t="n">
         <v>3.5</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.75</v>
-      </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O16" t="n">
         <v>4.33</v>
       </c>
       <c r="P16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q16" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q16" t="n">
-        <v>2.3</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="T16" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="U16" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="V16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X16" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.23</v>
+        <v>1.97</v>
       </c>
       <c r="AA16" t="n">
-        <v>2</v>
+        <v>2.86</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.78</v>
+        <v>1.45</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['86']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['5', '30', '36', '44']</t>
+          <t>['9', '29']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45554.57291666666</v>
@@ -2578,109 +2578,109 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N17" t="n">
         <v>2</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.1</v>
       </c>
       <c r="O17" t="n">
         <v>4.33</v>
       </c>
       <c r="P17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q17" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q17" t="n">
-        <v>2.4</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X17" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.97</v>
+        <v>2.23</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.86</v>
+        <v>2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.45</v>
+        <v>1.78</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['86']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['9', '29']</t>
+          <t>['5', '30', '36', '44']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45554.57291666666</v>
@@ -2697,97 +2697,97 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
         <v>2</v>
       </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>4.33</v>
-      </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>1.9</v>
+        <v>3.45</v>
       </c>
       <c r="O18" t="n">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="P18" t="n">
         <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.63</v>
+        <v>4.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>2.38</v>
+        <v>2.95</v>
       </c>
       <c r="T18" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="U18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.29</v>
       </c>
-      <c r="V18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.47</v>
-      </c>
       <c r="X18" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2796,20 +2796,20 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['65', '76']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.92</v>
+        <v>1.27</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.22</v>
+        <v>1.79</v>
       </c>
       <c r="AI18" t="n">
-        <v>3</v>
+        <v>1.68</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.57</v>
+        <v>2.35</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45554.58333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>2.33</v>
       </c>
       <c r="M19" t="n">
-        <v>14</v>
+        <v>3.65</v>
       </c>
       <c r="N19" t="n">
-        <v>23</v>
+        <v>2.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.18</v>
+        <v>2.86</v>
       </c>
       <c r="P19" t="n">
-        <v>4.75</v>
+        <v>2.35</v>
       </c>
       <c r="Q19" t="n">
-        <v>21</v>
+        <v>3.15</v>
       </c>
       <c r="R19" t="n">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>3.48</v>
       </c>
       <c r="T19" t="n">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="U19" t="n">
-        <v>3</v>
+        <v>1.58</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>13</v>
+        <v>4.55</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.25</v>
+        <v>2.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.2</v>
+        <v>2.45</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.33</v>
+        <v>1.55</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.38</v>
+        <v>1.49</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.53</v>
+        <v>2.51</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['24', '42', '65', '81']</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['64', '75']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH19" t="n">
-        <v>10</v>
+        <v>1.57</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.08</v>
+        <v>1.89</v>
       </c>
       <c r="AJ19" t="n">
-        <v>8</v>
+        <v>1.98</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45554.58333333334</v>
@@ -2955,26 +2955,26 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>2</v>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.33</v>
+        <v>4.33</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="O20" t="n">
-        <v>2.86</v>
+        <v>5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.15</v>
+        <v>2.63</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="S20" t="n">
-        <v>3.48</v>
+        <v>2.38</v>
       </c>
       <c r="T20" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.58</v>
+        <v>1.29</v>
       </c>
       <c r="V20" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>1.47</v>
       </c>
       <c r="X20" t="n">
-        <v>4.55</v>
+        <v>2.75</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.55</v>
+        <v>2.38</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.45</v>
+        <v>4.75</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.55</v>
+        <v>1.19</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.49</v>
+        <v>2.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.51</v>
+        <v>1.67</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['64', '75']</t>
+          <t>['65', '76']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.48</v>
+        <v>1.92</v>
       </c>
       <c r="AH20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.98</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45554.58333333334</v>
@@ -3084,119 +3084,119 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gefle</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="M21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q21" t="n">
         <v>5</v>
       </c>
-      <c r="N21" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>6.5</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="T21" t="n">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="U21" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X21" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB21" t="n">
+      <c r="AC21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['89', '90+8']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['12', '63']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AI21" t="n">
         <v>1.53</v>
       </c>
-      <c r="AC21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['90+4']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AJ21" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45554.58333333334</v>
@@ -3213,119 +3213,119 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Gefle</t>
         </is>
       </c>
       <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M22" t="n">
+        <v>5</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD22" t="n">
         <v>2</v>
       </c>
-      <c r="H22" t="n">
-        <v>2</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="M22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X22" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA22" t="n">
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH22" t="n">
         <v>2.95</v>
       </c>
-      <c r="AB22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>['89', '90+8']</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>['12', '63']</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>2.36</v>
-      </c>
       <c r="AI22" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45554.58333333334</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M23" t="n">
+        <v>5</v>
+      </c>
+      <c r="N23" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="O23" t="n">
         <v>2</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z23" t="n">
         <v>2.6</v>
       </c>
-      <c r="P23" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AA23" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11', '73']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['55', '63']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.79</v>
+        <v>2.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45554.58333333334</v>
@@ -3471,35 +3471,35 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.8</v>
+        <v>1.67</v>
       </c>
       <c r="M24" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="O24" t="n">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.88</v>
+        <v>6</v>
       </c>
       <c r="R24" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="S24" t="n">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="T24" t="n">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="U24" t="n">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1.17</v>
       </c>
-      <c r="X24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AC24" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.45</v>
+        <v>1.5</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['40', '60']</t>
+          <t>['11']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['45+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.66</v>
+        <v>1.11</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.11</v>
+        <v>1.44</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.79</v>
+        <v>3.75</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45554.58333333334</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,23 +3610,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
         <v>2</v>
       </c>
-      <c r="H25" t="n">
-        <v>2</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1</v>
-      </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="N25" t="n">
-        <v>6.25</v>
+        <v>23</v>
       </c>
       <c r="O25" t="n">
-        <v>2</v>
+        <v>1.18</v>
       </c>
       <c r="P25" t="n">
-        <v>2.63</v>
+        <v>4.75</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="R25" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T25" t="n">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="U25" t="n">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="V25" t="n">
         <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>5.5</v>
+        <v>13</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.44</v>
+        <v>1.06</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.6</v>
+        <v>7.25</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.73</v>
+        <v>4.33</v>
       </c>
       <c r="AC25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.53</v>
       </c>
-      <c r="AD25" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['11', '73']</t>
+          <t>['24', '42', '65', '81']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['55', '63']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AJ25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45554.58333333334</v>
@@ -3729,35 +3729,35 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="n">
         <v>1</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.67</v>
+        <v>2.8</v>
       </c>
       <c r="M26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA26" t="n">
         <v>3</v>
       </c>
-      <c r="N26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>6</v>
-      </c>
-      <c r="R26" t="n">
+      <c r="AB26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC26" t="n">
         <v>1.53</v>
       </c>
-      <c r="S26" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AD26" t="n">
-        <v>1.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['11']</t>
+          <t>['40', '60']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+1']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.44</v>
+        <v>2.11</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3.75</v>
+        <v>1.79</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45554.58333333334</v>
@@ -4126,25 +4126,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4</v>
+        <v>1.85</v>
       </c>
       <c r="M29" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N29" t="n">
-        <v>1.83</v>
+        <v>4.33</v>
       </c>
       <c r="O29" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="P29" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="R29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W29" t="n">
         <v>1.33</v>
       </c>
-      <c r="S29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.24</v>
-      </c>
       <c r="X29" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.12</v>
+        <v>1.86</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.89</v>
+        <v>3.55</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23', '56']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+1']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.96</v>
+        <v>1.23</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.27</v>
+        <v>2.03</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.5</v>
+        <v>1.53</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.57</v>
+        <v>2.75</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45554.66666666666</v>
@@ -4384,25 +4384,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.85</v>
+        <v>4</v>
       </c>
       <c r="M31" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="N31" t="n">
-        <v>4.33</v>
+        <v>1.83</v>
       </c>
       <c r="O31" t="n">
+        <v>4</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q31" t="n">
         <v>2.5</v>
       </c>
-      <c r="P31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>4.5</v>
-      </c>
       <c r="R31" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="T31" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U31" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V31" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W31" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="X31" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.55</v>
+        <v>2.89</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['23', '56']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['45+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.23</v>
+        <v>1.96</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.03</v>
+        <v>1.27</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.75</v>
+        <v>1.57</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45554.66666666666</v>
